--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,44 +19,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+  <x:si>
+    <x:t>상대1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
   <x:si>
     <x:t>fighter_02</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Def</x:t>
+  </x:si>
+  <x:si>
     <x:t>Atk</x:t>
   </x:si>
   <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>Hp</x:t>
   </x:si>
   <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Def</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
+    <x:t>상대2</x:t>
   </x:si>
   <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 적이다</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
@@ -66,7 +72,19 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_01</x:t>
+    <x:t>기본 상대2이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -852,58 +870,58 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>100</x:v>
@@ -917,13 +935,13 @@
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>150</x:v>
@@ -935,15 +953,45 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A6" s="5"/>
-      <x:c r="B6" s="5"/>
-      <x:c r="C6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="5"/>
-      <x:c r="C7" s="5"/>
+    <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A6" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="1">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E6" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="1">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A7" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D7" s="1">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E7" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" s="1">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A8" s="5"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,72 +19,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대2이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
   <x:si>
     <x:t>상대1</x:t>
   </x:si>
   <x:si>
-    <x:t>상대3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Atk</x:t>
   </x:si>
   <x:si>
     <x:t>Def</x:t>
   </x:si>
   <x:si>
-    <x:t>Atk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대2이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
+    <x:t>상대4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대4이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대5이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대6이다</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -870,58 +897,58 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>100</x:v>
@@ -935,13 +962,13 @@
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>150</x:v>
@@ -955,13 +982,13 @@
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>170</x:v>
@@ -975,13 +1002,13 @@
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>250</x:v>
@@ -993,17 +1020,66 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5"/>
-      <x:c r="B8" s="5"/>
-      <x:c r="C8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5"/>
-      <x:c r="C9" s="5"/>
-    </x:row>
-    <x:row r="10" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="1">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E8" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="1">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D9" s="1">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="E9" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="1">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D10" s="1">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E10" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="1">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A12" s="6"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -21,97 +21,97 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <x:si>
+    <x:t>Atk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Def</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
     <x:t>fighter_05</x:t>
   </x:si>
   <x:si>
-    <x:t>상대5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>기본 캐릭터이다</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_01</x:t>
+    <x:t>기본 상대4이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대6이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대5이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
+  </x:si>
+  <x:si>
     <x:t>fighter_03</x:t>
   </x:si>
   <x:si>
     <x:t>기본 상대2이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Atk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Def</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대4이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대5이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대6이다</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -897,58 +897,58 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>100</x:v>
@@ -962,13 +962,13 @@
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>150</x:v>
@@ -982,13 +982,13 @@
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>170</x:v>
@@ -1002,13 +1002,13 @@
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>250</x:v>
@@ -1022,13 +1022,13 @@
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>270</x:v>
@@ -1042,13 +1042,13 @@
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>300</x:v>
@@ -1062,22 +1062,22 @@
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>350</x:v>
       </x:c>
       <x:c r="E10" s="1">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,99 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+  <x:si>
+    <x:t>PortraitAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Def</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
   <x:si>
     <x:t>Atk</x:t>
   </x:si>
   <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대6</x:t>
+  </x:si>
+  <x:si>
     <x:t>상대5</x:t>
   </x:si>
   <x:si>
-    <x:t>상대3</x:t>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
   </x:si>
   <x:si>
     <x:t>상대4</x:t>
   </x:si>
   <x:si>
-    <x:t>Def</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
+    <x:t>KimBasic[south-east 1_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대5이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대2이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대4이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대6이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대4이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대6이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대5이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대2이다</x:t>
+    <x:t>KimBasic[south-east 1_0]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -882,316 +897,414 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:F35"/>
+  <x:dimension ref="A1:H35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="50.7265625" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="20.26953125" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <x:col min="8" max="16384" width="12.54296875" style="1"/>
+    <x:col min="4" max="6" width="20.26953125" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="30.54296875" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="26.54296875" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="20" style="1" customWidth="1"/>
+    <x:col min="10" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
+      <x:c r="E4" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F4" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G4" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="H4" s="4">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E4" s="1">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="4">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="5" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F5" s="1">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G5" s="1">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H5" s="1">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="1">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E5" s="1">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F5" s="1">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="6" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F6" s="1">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G6" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H6" s="1">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A7" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F7" s="1">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G7" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H7" s="1">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F8" s="1">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G8" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="1">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="1">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="E6" s="1">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="1">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A7" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D7" s="1">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="E7" s="1">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="1">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D8" s="1">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="E8" s="1">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="1">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D9" s="1">
+      <x:c r="D9" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F9" s="1">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="E9" s="1">
+      <x:c r="G9" s="1">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="1">
+      <x:c r="H9" s="1">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="10" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="1">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F10" s="1">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="E10" s="1">
+      <x:c r="G10" s="1">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F10" s="1">
+      <x:c r="H10" s="1">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="12" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="6"/>
       <x:c r="C12" s="6"/>
-    </x:row>
-    <x:row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A13" s="3"/>
       <x:c r="B13" s="3"/>
       <x:c r="C13" s="3"/>
+      <x:c r="D13" s="3"/>
+      <x:c r="E13" s="3"/>
     </x:row>
     <x:row r="14" ht="15.75" customHeight="1"/>
     <x:row r="15" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="5"/>
       <x:c r="B16" s="5"/>
       <x:c r="C16" s="5"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D16" s="5"/>
+      <x:c r="E16" s="5"/>
+    </x:row>
+    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="5"/>
       <x:c r="B17" s="5"/>
       <x:c r="C17" s="5"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D17" s="5"/>
+      <x:c r="E17" s="5"/>
+    </x:row>
+    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="5"/>
       <x:c r="B18" s="5"/>
       <x:c r="C18" s="5"/>
-    </x:row>
-    <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D18" s="5"/>
+      <x:c r="E18" s="5"/>
+    </x:row>
+    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="5"/>
       <x:c r="B19" s="5"/>
       <x:c r="C19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D19" s="5"/>
+      <x:c r="E19" s="5"/>
+    </x:row>
+    <x:row r="20" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A20" s="5"/>
       <x:c r="B20" s="5"/>
       <x:c r="C20" s="5"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D20" s="5"/>
+      <x:c r="E20" s="5"/>
+    </x:row>
+    <x:row r="21" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A21" s="5"/>
       <x:c r="B21" s="5"/>
       <x:c r="C21" s="5"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D21" s="5"/>
+      <x:c r="E21" s="5"/>
+    </x:row>
+    <x:row r="22" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A22" s="5"/>
       <x:c r="B22" s="5"/>
       <x:c r="C22" s="5"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D22" s="5"/>
+      <x:c r="E22" s="5"/>
+    </x:row>
+    <x:row r="23" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A23" s="5"/>
       <x:c r="B23" s="5"/>
       <x:c r="C23" s="5"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D23" s="5"/>
+      <x:c r="E23" s="5"/>
+    </x:row>
+    <x:row r="24" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A24" s="5"/>
       <x:c r="B24" s="5"/>
       <x:c r="C24" s="5"/>
-    </x:row>
-    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D24" s="5"/>
+      <x:c r="E24" s="5"/>
+    </x:row>
+    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A25" s="5"/>
       <x:c r="B25" s="5"/>
       <x:c r="C25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D25" s="5"/>
+      <x:c r="E25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A26" s="6"/>
       <x:c r="B26" s="6"/>
       <x:c r="C26" s="6"/>
-    </x:row>
-    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D26" s="6"/>
+      <x:c r="E26" s="6"/>
+    </x:row>
+    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A27" s="6"/>
       <x:c r="B27" s="6"/>
       <x:c r="C27" s="6"/>
-    </x:row>
-    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D27" s="6"/>
+      <x:c r="E27" s="6"/>
+    </x:row>
+    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A28" s="6"/>
       <x:c r="B28" s="6"/>
       <x:c r="C28" s="6"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D28" s="6"/>
+      <x:c r="E28" s="6"/>
+    </x:row>
+    <x:row r="29" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A29" s="6"/>
       <x:c r="B29" s="6"/>
       <x:c r="C29" s="6"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D29" s="6"/>
+      <x:c r="E29" s="6"/>
+    </x:row>
+    <x:row r="30" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A30" s="6"/>
       <x:c r="B30" s="6"/>
       <x:c r="C30" s="6"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D30" s="6"/>
+      <x:c r="E30" s="6"/>
+    </x:row>
+    <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A31" s="6"/>
       <x:c r="B31" s="6"/>
       <x:c r="C31" s="6"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D31" s="6"/>
+      <x:c r="E31" s="6"/>
+    </x:row>
+    <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A32" s="3"/>
       <x:c r="B32" s="3"/>
       <x:c r="C32" s="3"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D32" s="3"/>
+      <x:c r="E32" s="3"/>
+    </x:row>
+    <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A33" s="3"/>
       <x:c r="B33" s="3"/>
       <x:c r="C33" s="3"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D33" s="3"/>
+      <x:c r="E33" s="3"/>
+    </x:row>
+    <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A34" s="3"/>
       <x:c r="B34" s="3"/>
       <x:c r="C34" s="3"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D34" s="3"/>
+      <x:c r="E34" s="3"/>
+    </x:row>
+    <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A35" s="3"/>
       <x:c r="B35" s="3"/>
       <x:c r="C35" s="3"/>
+      <x:c r="D35" s="3"/>
+      <x:c r="E35" s="3"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,111 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <x:si>
     <x:t>PortraitAddress</x:t>
   </x:si>
   <x:si>
+    <x:t>상대6</x:t>
+  </x:si>
+  <x:si>
     <x:t>Def</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>상대4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Atk</x:t>
   </x:si>
   <x:si>
-    <x:t>상대3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대5</x:t>
-  </x:si>
-  <x:si>
     <x:t>김기본</x:t>
   </x:si>
   <x:si>
-    <x:t>상대1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대4</x:t>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대2이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대4이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대6이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대5이다</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대5이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대2이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대4이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대6이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_0]</x:t>
@@ -897,7 +900,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:H35"/>
+  <x:dimension ref="A1:I35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -912,76 +915,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.199999999999999">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="7" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>100</x:v>
@@ -992,22 +1001,25 @@
       <x:c r="H4" s="4">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="I4" s="1">
+        <x:v>100</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1021,19 +1033,19 @@
     </x:row>
     <x:row r="6" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1047,19 +1059,19 @@
     </x:row>
     <x:row r="7" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1073,19 +1085,19 @@
     </x:row>
     <x:row r="8" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1099,19 +1111,19 @@
     </x:row>
     <x:row r="9" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1125,19 +1137,19 @@
     </x:row>
     <x:row r="10" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,111 +19,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대5이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대2이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대4이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대6이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingOffense</x:t>
+  </x:si>
   <x:si>
     <x:t>PortraitAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Def</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Atk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대2이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대4이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대6이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대5이다</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_1]</x:t>
@@ -900,7 +915,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I35"/>
+  <x:dimension ref="A1:N35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -910,255 +925,413 @@
     <x:col min="7" max="7" width="30.54296875" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="26.54296875" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <x:col min="10" max="16384" width="12.54296875" style="1"/>
+    <x:col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
+    <x:col min="11" max="12" width="18" style="1" customWidth="1"/>
+    <x:col min="13" max="13" width="18.85546875" style="1" customWidth="1"/>
+    <x:col min="14" max="14" width="18.4296875" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="17.14453125" style="1" customWidth="1"/>
+    <x:col min="16" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="13.199999999999999">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>6</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>2</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="G4" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H4" s="4">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="I4" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J4" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K4" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L4" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M4" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N4" s="1">
         <x:v>100</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="5" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
       </x:c>
       <x:c r="G5" s="1">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H5" s="1">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H5" s="1">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I5" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J5" s="1">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K5" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L5" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M5" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
       </x:c>
       <x:c r="G6" s="1">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H6" s="1">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H6" s="1">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I6" s="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J6" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K6" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M6" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
       </x:c>
       <x:c r="G7" s="1">
-        <x:v>20</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H7" s="1">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I7" s="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J7" s="1">
         <x:v>10</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="K7" s="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L7" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M7" s="1">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
       </x:c>
       <x:c r="G8" s="1">
-        <x:v>18</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H8" s="1">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="I8" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J8" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K8" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L8" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M8" s="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="G9" s="1">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H9" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I9" s="1">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H9" s="1">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="J9" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K9" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L9" s="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M9" s="1">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="N9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
       </x:c>
       <x:c r="G10" s="1">
-        <x:v>70</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I10" s="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J10" s="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K10" s="1">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L10" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M10" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N10" s="1">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,126 +19,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대3이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대6이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대1이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대4이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대2이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 상대5이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartingSkillIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
   <x:si>
     <x:t>WrestlingDefense</x:t>
   </x:si>
   <x:si>
-    <x:t>WrestlingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대5이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 상대2이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대4이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대6이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
+    <x:t>skill_jab,skill_elbow,skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PortraitAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>김기본</x:t>
   </x:si>
   <x:si>
-    <x:t>상대1</x:t>
-  </x:si>
-  <x:si>
     <x:t>상대2</x:t>
   </x:si>
   <x:si>
     <x:t>상대4</x:t>
   </x:si>
   <x:si>
-    <x:t>상대3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대6</x:t>
+    <x:t>상대5</x:t>
   </x:si>
   <x:si>
     <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PortraitAddress</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_1]</x:t>
@@ -915,7 +921,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:N35"/>
+  <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
@@ -935,112 +941,118 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:15" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="D3" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="M2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>100</x:v>
@@ -1069,22 +1081,25 @@
       <x:c r="N4" s="1">
         <x:v>100</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O4" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1113,22 +1128,25 @@
       <x:c r="N5" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O5" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1157,22 +1175,25 @@
       <x:c r="N6" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1201,22 +1222,25 @@
       <x:c r="N7" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O7" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1245,22 +1269,25 @@
       <x:c r="N8" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O8" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1289,22 +1316,25 @@
       <x:c r="N9" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O9" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1332,6 +1362,9 @@
       </x:c>
       <x:c r="N10" s="1">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="1" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,138 +19,153 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartingSkillIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
   <x:si>
     <x:t>fighter_02</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대3이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
   </x:si>
   <x:si>
     <x:t>기본 캐릭터이다</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 상대6이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대1이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대4이다</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
     <x:t>fighter_07</x:t>
   </x:si>
   <x:si>
-    <x:t>기본 상대2이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 상대5이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartingSkillIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingDefense</x:t>
+    <x:t>김종합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링과 Ground 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PortraitAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격, 테이크다운 방어 위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현된 특수기술 전체 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
   </x:si>
   <x:si>
     <x:t>float</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션 스트릭랜드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주짓수위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김레슬러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김주짓수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김클린치</x:t>
+  </x:si>
+  <x:si>
     <x:t>Stamina</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
+    <x:t>김그래플러</x:t>
   </x:si>
   <x:si>
     <x:t>None</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab,skill_elbow,skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PortraitAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KimBasic[south-east 1_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_1]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_0]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -941,165 +956,165 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:15" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K3" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L3" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M3" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="1">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H4" s="4">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="1">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J4" s="1">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="1">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L4" s="1">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M4" s="1">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="N4" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1114,10 +1129,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="J5" s="1">
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K5" s="1">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L5" s="1">
         <x:v>10</x:v>
@@ -1129,24 +1144,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1161,39 +1176,39 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="J6" s="1">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K6" s="1">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L6" s="1">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M6" s="1">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N6" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1202,13 +1217,13 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>15</x:v>
       </x:c>
       <x:c r="J7" s="1">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K7" s="1">
         <x:v>15</x:v>
@@ -1223,24 +1238,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1249,45 +1264,45 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="H8" s="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I8" s="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J8" s="1">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I8" s="1">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J8" s="1">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="K8" s="1">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L8" s="1">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="1">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="N8" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1302,39 +1317,39 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="J9" s="1">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K9" s="1">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L9" s="1">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M9" s="1">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N9" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1343,31 +1358,77 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>35</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J10" s="1">
         <x:v>35</x:v>
       </x:c>
       <x:c r="K10" s="1">
-        <x:v>30</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="L10" s="1">
         <x:v>25</x:v>
       </x:c>
       <x:c r="M10" s="1">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="N10" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15.75" customHeight="1"/>
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A11" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F11" s="1">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G11" s="1">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H11" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I11" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J11" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K11" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L11" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M11" s="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N11" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="6"/>

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -19,153 +19,159 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
+  <x:si>
+    <x:t>김기본</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김종합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BodyAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 캐릭터이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
   <x:si>
     <x:t>WrestlingDefense</x:t>
   </x:si>
   <x:si>
-    <x:t>WrestlingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
     <x:t>StartingSkillIds</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 캐릭터이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BodyAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김종합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김타격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김기본</x:t>
+    <x:t>주짓수위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김레슬러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김주짓수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션 스트릭랜드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김그래플러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김클린치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KimBasic[south-east 1_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KimBasic[south-east 1_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
   </x:si>
   <x:si>
     <x:t>레슬링과 Ground 테스트</x:t>
   </x:si>
   <x:si>
+    <x:t>타격, 테이크다운 방어 위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
     <x:t>PortraitAddress</x:t>
   </x:si>
   <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
     <x:t>JiuJitsuDefense</x:t>
   </x:si>
   <x:si>
-    <x:t>타격, 테이크다운 방어 위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
     <x:t>구현된 특수기술 전체 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션 스트릭랜드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주짓수위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김레슬러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김주짓수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김클린치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김그래플러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_0]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KimBasic[south-east 1_1]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -956,24 +962,24 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:15" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
         <x:v>30</x:v>
@@ -1003,71 +1009,71 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>150</x:v>
@@ -1097,7 +1103,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
@@ -1105,16 +1111,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1144,24 +1150,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1191,24 +1197,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1238,24 +1244,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1285,24 +1291,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D9" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1332,24 +1338,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1379,24 +1385,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>400</x:v>
@@ -1426,7 +1432,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/FighterData.xlsx
+++ b/JsonConverter/ExcelFiles/FighterData.xlsx
@@ -21,121 +21,148 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
   <x:si>
+    <x:t>김종합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김타격</x:t>
+  </x:si>
+  <x:si>
     <x:t>김기본</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>Hp</x:t>
   </x:si>
   <x:si>
-    <x:t>김종합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김타격</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartingSkillIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fighter_04</x:t>
   </x:si>
   <x:si>
     <x:t>fighter_07</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>fighter_08</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_02</x:t>
+    <x:t>fighter_01</x:t>
   </x:si>
   <x:si>
     <x:t>BodyAddress</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>기본 캐릭터이다</x:t>
   </x:si>
   <x:si>
-    <x:t>fighter_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fighter_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow,skill_uppercut,skill_takedown_judo</x:t>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주짓수위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김클린치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김레슬러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션 스트릭랜드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김그래플러</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김주짓수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치위주</x:t>
   </x:si>
   <x:si>
     <x:t>skill_elbow,skill_uppercut,skill_takedown_judo,skill_guillotine</x:t>
   </x:si>
   <x:si>
-    <x:t>WrestlingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StartingSkillIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주짓수위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김레슬러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김주짓수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션 스트릭랜드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김그래플러</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>김클린치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현된 특수기술 전체 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링과 Ground 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타격, 테이크다운 방어 위주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PortraitAddress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
   </x:si>
   <x:si>
     <x:t>KimBasic[south-east 1_0]</x:t>
@@ -145,33 +172,6 @@
   </x:si>
   <x:si>
     <x:t>skill_elbow,skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링과 Ground 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격, 테이크다운 방어 위주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PortraitAddress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구현된 특수기술 전체 테스트</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -962,118 +962,118 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:15" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:15" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
+      <x:c r="G3" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="L3" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="M3" s="7" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="N3" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>150</x:v>
@@ -1103,24 +1103,24 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>150</x:v>
@@ -1150,24 +1150,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E6" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>170</x:v>
@@ -1197,24 +1197,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>250</x:v>
@@ -1244,24 +1244,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>270</x:v>
@@ -1291,24 +1291,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="E9" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
@@ -1338,24 +1338,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>350</x:v>
@@ -1385,24 +1385,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>400</x:v>
@@ -1432,7 +1432,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" ht="15.75" customHeight="1">
